--- a/db/tablas_procesadas/Curso.xlsx
+++ b/db/tablas_procesadas/Curso.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PosGrado\Proyecto Titulacion\Timetabling\db\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andre\Documents\Posgrado\Proyecto Titulacion\db\tablas_procesadas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{982C153E-429B-479B-B1CA-A356C525CAF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B27DF4B2-6AA8-4C98-85B3-199D56F1B937}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3285" yWindow="4005" windowWidth="28785" windowHeight="15345" xr2:uid="{BF92CB84-5E73-48F7-873C-5BA243B34C6E}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{BF92CB84-5E73-48F7-873C-5BA243B34C6E}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -208,7 +208,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -575,15 +575,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3253D992-7E52-448D-BED3-7C5D72D55D53}">
   <dimension ref="A1:F23"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="13" customWidth="1"/>
-    <col min="4" max="4" width="13.25" customWidth="1"/>
-    <col min="5" max="5" width="11.875" customWidth="1"/>
-    <col min="6" max="6" width="14.625" customWidth="1"/>
+    <col min="4" max="4" width="13.21875" customWidth="1"/>
+    <col min="5" max="5" width="11.88671875" customWidth="1"/>
+    <col min="6" max="6" width="14.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -603,7 +603,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>23</v>
       </c>
@@ -623,7 +623,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>24</v>
       </c>
@@ -643,7 +643,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>25</v>
       </c>
@@ -663,7 +663,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>26</v>
       </c>
@@ -683,7 +683,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>27</v>
       </c>
@@ -703,7 +703,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>28</v>
       </c>
@@ -723,7 +723,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>29</v>
       </c>
@@ -743,7 +743,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>30</v>
       </c>
@@ -763,7 +763,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>31</v>
       </c>
@@ -783,7 +783,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>32</v>
       </c>
@@ -803,7 +803,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="1:6">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>33</v>
       </c>
@@ -823,7 +823,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:6">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>34</v>
       </c>
@@ -843,7 +843,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="14" spans="1:6">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>36</v>
       </c>
@@ -863,7 +863,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="15" spans="1:6">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>35</v>
       </c>
@@ -883,7 +883,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:6">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>37</v>
       </c>
@@ -903,7 +903,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="17" spans="1:6">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>38</v>
       </c>
@@ -923,7 +923,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="18" spans="1:6">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>39</v>
       </c>
@@ -943,7 +943,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="19" spans="1:6">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>40</v>
       </c>
@@ -963,7 +963,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="20" spans="1:6">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>41</v>
       </c>
@@ -983,7 +983,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="21" spans="1:6">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>42</v>
       </c>
@@ -1003,7 +1003,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="22" spans="1:6">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>43</v>
       </c>
@@ -1023,7 +1023,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="23" spans="1:6">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>53</v>
       </c>

--- a/db/tablas_procesadas/Curso.xlsx
+++ b/db/tablas_procesadas/Curso.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andre\Documents\Posgrado\Proyecto Titulacion\db\tablas_procesadas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PosGrado\Proyecto Titulacion\Timetabling\db\tablas_procesadas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B27DF4B2-6AA8-4C98-85B3-199D56F1B937}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11111D2E-91C7-4A27-B951-AF83218DB9AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{BF92CB84-5E73-48F7-873C-5BA243B34C6E}"/>
+    <workbookView xWindow="7965" yWindow="3480" windowWidth="28785" windowHeight="15345" xr2:uid="{BF92CB84-5E73-48F7-873C-5BA243B34C6E}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="54">
   <si>
     <t>curso_id</t>
   </si>
@@ -184,12 +184,6 @@
   </si>
   <si>
     <t>Intermedio</t>
-  </si>
-  <si>
-    <t>horario_entrada</t>
-  </si>
-  <si>
-    <t>horario_salida</t>
   </si>
   <si>
     <t>3°Ini-3°Int</t>
@@ -208,7 +202,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -237,9 +231,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -574,16 +567,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3253D992-7E52-448D-BED3-7C5D72D55D53}">
-  <dimension ref="A1:F23"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:D23"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="13" customWidth="1"/>
-    <col min="4" max="4" width="13.21875" customWidth="1"/>
-    <col min="5" max="5" width="11.88671875" customWidth="1"/>
-    <col min="6" max="6" width="14.6640625" customWidth="1"/>
+    <col min="4" max="4" width="14.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -594,16 +585,10 @@
         <v>44</v>
       </c>
       <c r="D1" t="s">
-        <v>50</v>
-      </c>
-      <c r="E1" t="s">
-        <v>51</v>
-      </c>
-      <c r="F1" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
       <c r="A2" t="s">
         <v>23</v>
       </c>
@@ -613,17 +598,11 @@
       <c r="C2" t="s">
         <v>45</v>
       </c>
-      <c r="D2" s="1">
-        <v>0.625</v>
-      </c>
-      <c r="E2" s="1">
-        <v>0.75</v>
-      </c>
-      <c r="F2">
+      <c r="D2">
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4">
       <c r="A3" t="s">
         <v>24</v>
       </c>
@@ -633,17 +612,11 @@
       <c r="C3" t="s">
         <v>45</v>
       </c>
-      <c r="D3" s="1">
-        <v>0.625</v>
-      </c>
-      <c r="E3" s="1">
-        <v>0.75</v>
-      </c>
-      <c r="F3">
+      <c r="D3">
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4">
       <c r="A4" t="s">
         <v>25</v>
       </c>
@@ -653,17 +626,11 @@
       <c r="C4" t="s">
         <v>45</v>
       </c>
-      <c r="D4" s="1">
-        <v>0.625</v>
-      </c>
-      <c r="E4" s="1">
-        <v>0.75</v>
-      </c>
-      <c r="F4">
+      <c r="D4">
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4">
       <c r="A5" t="s">
         <v>26</v>
       </c>
@@ -673,17 +640,11 @@
       <c r="C5" t="s">
         <v>45</v>
       </c>
-      <c r="D5" s="1">
-        <v>0.625</v>
-      </c>
-      <c r="E5" s="1">
-        <v>0.75</v>
-      </c>
-      <c r="F5">
+      <c r="D5">
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4">
       <c r="A6" t="s">
         <v>27</v>
       </c>
@@ -693,17 +654,11 @@
       <c r="C6" t="s">
         <v>45</v>
       </c>
-      <c r="D6" s="1">
-        <v>0.625</v>
-      </c>
-      <c r="E6" s="1">
-        <v>0.75</v>
-      </c>
-      <c r="F6">
+      <c r="D6">
         <v>23</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4">
       <c r="A7" t="s">
         <v>28</v>
       </c>
@@ -713,17 +668,11 @@
       <c r="C7" t="s">
         <v>45</v>
       </c>
-      <c r="D7" s="1">
-        <v>0.625</v>
-      </c>
-      <c r="E7" s="1">
-        <v>0.75</v>
-      </c>
-      <c r="F7">
+      <c r="D7">
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4">
       <c r="A8" t="s">
         <v>29</v>
       </c>
@@ -733,17 +682,11 @@
       <c r="C8" t="s">
         <v>46</v>
       </c>
-      <c r="D8" s="1">
-        <v>0.625</v>
-      </c>
-      <c r="E8" s="1">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="F8">
+      <c r="D8">
         <v>29</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4">
       <c r="A9" t="s">
         <v>30</v>
       </c>
@@ -753,17 +696,11 @@
       <c r="C9" t="s">
         <v>46</v>
       </c>
-      <c r="D9" s="1">
-        <v>0.625</v>
-      </c>
-      <c r="E9" s="1">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="F9">
+      <c r="D9">
         <v>28</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4">
       <c r="A10" t="s">
         <v>31</v>
       </c>
@@ -773,17 +710,11 @@
       <c r="C10" t="s">
         <v>46</v>
       </c>
-      <c r="D10" s="1">
-        <v>0.625</v>
-      </c>
-      <c r="E10" s="1">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="F10">
+      <c r="D10">
         <v>21</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4">
       <c r="A11" t="s">
         <v>32</v>
       </c>
@@ -793,17 +724,11 @@
       <c r="C11" t="s">
         <v>46</v>
       </c>
-      <c r="D11" s="1">
-        <v>0.625</v>
-      </c>
-      <c r="E11" s="1">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="F11">
+      <c r="D11">
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4">
       <c r="A12" t="s">
         <v>33</v>
       </c>
@@ -813,17 +738,11 @@
       <c r="C12" t="s">
         <v>46</v>
       </c>
-      <c r="D12" s="1">
-        <v>0.625</v>
-      </c>
-      <c r="E12" s="1">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="F12">
+      <c r="D12">
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4">
       <c r="A13" t="s">
         <v>34</v>
       </c>
@@ -833,17 +752,11 @@
       <c r="C13" t="s">
         <v>47</v>
       </c>
-      <c r="D13" s="1">
-        <v>0.625</v>
-      </c>
-      <c r="E13" s="1">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="F13">
+      <c r="D13">
         <v>29</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4">
       <c r="A14" t="s">
         <v>36</v>
       </c>
@@ -853,17 +766,11 @@
       <c r="C14" t="s">
         <v>47</v>
       </c>
-      <c r="D14" s="1">
-        <v>0.625</v>
-      </c>
-      <c r="E14" s="1">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="F14">
+      <c r="D14">
         <v>28</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4">
       <c r="A15" t="s">
         <v>35</v>
       </c>
@@ -873,17 +780,11 @@
       <c r="C15" t="s">
         <v>47</v>
       </c>
-      <c r="D15" s="1">
-        <v>0.625</v>
-      </c>
-      <c r="E15" s="1">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="F15">
+      <c r="D15">
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4">
       <c r="A16" t="s">
         <v>37</v>
       </c>
@@ -893,17 +794,11 @@
       <c r="C16" t="s">
         <v>48</v>
       </c>
-      <c r="D16" s="1">
-        <v>0.70833333333333337</v>
-      </c>
-      <c r="E16" s="1">
-        <v>0.875</v>
-      </c>
-      <c r="F16">
+      <c r="D16">
         <v>32</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4">
       <c r="A17" t="s">
         <v>38</v>
       </c>
@@ -913,17 +808,11 @@
       <c r="C17" t="s">
         <v>48</v>
       </c>
-      <c r="D17" s="1">
-        <v>0.70833333333333337</v>
-      </c>
-      <c r="E17" s="1">
-        <v>0.875</v>
-      </c>
-      <c r="F17">
+      <c r="D17">
         <v>32</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4">
       <c r="A18" t="s">
         <v>39</v>
       </c>
@@ -933,17 +822,11 @@
       <c r="C18" t="s">
         <v>48</v>
       </c>
-      <c r="D18" s="1">
-        <v>0.70833333333333337</v>
-      </c>
-      <c r="E18" s="1">
-        <v>0.875</v>
-      </c>
-      <c r="F18">
+      <c r="D18">
         <v>32</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4">
       <c r="A19" t="s">
         <v>40</v>
       </c>
@@ -953,17 +836,11 @@
       <c r="C19" t="s">
         <v>48</v>
       </c>
-      <c r="D19" s="1">
-        <v>0.70833333333333337</v>
-      </c>
-      <c r="E19" s="1">
-        <v>0.875</v>
-      </c>
-      <c r="F19">
+      <c r="D19">
         <v>33</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4">
       <c r="A20" t="s">
         <v>41</v>
       </c>
@@ -973,17 +850,11 @@
       <c r="C20" t="s">
         <v>49</v>
       </c>
-      <c r="D20" s="1">
-        <v>0.70833333333333337</v>
-      </c>
-      <c r="E20" s="1">
-        <v>0.875</v>
-      </c>
-      <c r="F20">
+      <c r="D20">
         <v>27</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4">
       <c r="A21" t="s">
         <v>42</v>
       </c>
@@ -993,17 +864,11 @@
       <c r="C21" t="s">
         <v>49</v>
       </c>
-      <c r="D21" s="1">
-        <v>0.70833333333333337</v>
-      </c>
-      <c r="E21" s="1">
-        <v>0.875</v>
-      </c>
-      <c r="F21">
+      <c r="D21">
         <v>17</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4">
       <c r="A22" t="s">
         <v>43</v>
       </c>
@@ -1013,33 +878,21 @@
       <c r="C22" t="s">
         <v>49</v>
       </c>
-      <c r="D22" s="1">
-        <v>0.70833333333333337</v>
-      </c>
-      <c r="E22" s="1">
-        <v>0.875</v>
-      </c>
-      <c r="F22">
+      <c r="D22">
         <v>7</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4">
       <c r="A23" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B23" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C23" t="s">
-        <v>52</v>
-      </c>
-      <c r="D23" s="1">
-        <v>0.625</v>
-      </c>
-      <c r="E23" s="1">
-        <v>0.875</v>
-      </c>
-      <c r="F23">
+        <v>50</v>
+      </c>
+      <c r="D23">
         <v>200</v>
       </c>
     </row>

--- a/db/tablas_procesadas/Curso.xlsx
+++ b/db/tablas_procesadas/Curso.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PosGrado\Proyecto Titulacion\Timetabling\db\tablas_procesadas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11111D2E-91C7-4A27-B951-AF83218DB9AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70D425EA-C16C-47B3-B952-5C8C3D663097}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7965" yWindow="3480" windowWidth="28785" windowHeight="15345" xr2:uid="{BF92CB84-5E73-48F7-873C-5BA243B34C6E}"/>
   </bookViews>
@@ -34,14 +34,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="78">
   <si>
     <t>curso_id</t>
   </si>
   <si>
-    <t>nombre_curso</t>
-  </si>
-  <si>
     <t>1°Infantil (A)</t>
   </si>
   <si>
@@ -196,16 +193,97 @@
   </si>
   <si>
     <t>inscritos</t>
+  </si>
+  <si>
+    <t>detalle</t>
+  </si>
+  <si>
+    <t>curso</t>
+  </si>
+  <si>
+    <t>G1</t>
+  </si>
+  <si>
+    <t>G2</t>
+  </si>
+  <si>
+    <t>G3</t>
+  </si>
+  <si>
+    <t>G4</t>
+  </si>
+  <si>
+    <t>G5</t>
+  </si>
+  <si>
+    <t>G6</t>
+  </si>
+  <si>
+    <t>G7</t>
+  </si>
+  <si>
+    <t>G8</t>
+  </si>
+  <si>
+    <t>G9</t>
+  </si>
+  <si>
+    <t>G10</t>
+  </si>
+  <si>
+    <t>G11</t>
+  </si>
+  <si>
+    <t>G12</t>
+  </si>
+  <si>
+    <t>G13</t>
+  </si>
+  <si>
+    <t>G14</t>
+  </si>
+  <si>
+    <t>G15</t>
+  </si>
+  <si>
+    <t>G16</t>
+  </si>
+  <si>
+    <t>G17</t>
+  </si>
+  <si>
+    <t>G18</t>
+  </si>
+  <si>
+    <t>G19</t>
+  </si>
+  <si>
+    <t>G20</t>
+  </si>
+  <si>
+    <t>G21</t>
+  </si>
+  <si>
+    <t>G22</t>
+  </si>
+  <si>
+    <t>contar</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -567,336 +645,475 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3253D992-7E52-448D-BED3-7C5D72D55D53}">
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25"/>
   <cols>
-    <col min="2" max="2" width="13" customWidth="1"/>
-    <col min="4" max="4" width="14.625" customWidth="1"/>
+    <col min="3" max="3" width="13" customWidth="1"/>
+    <col min="5" max="5" width="14.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E1" t="s">
+        <v>52</v>
+      </c>
+      <c r="F1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D2" t="s">
         <v>44</v>
       </c>
-      <c r="D1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
-      <c r="A2" t="s">
+      <c r="E2">
+        <v>15</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B3" t="s">
         <v>23</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C3" t="s">
         <v>2</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E3">
+        <v>15</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" t="s">
+        <v>44</v>
+      </c>
+      <c r="E4">
+        <v>18</v>
+      </c>
+      <c r="F4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" t="s">
+        <v>58</v>
+      </c>
+      <c r="B5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D5" t="s">
+        <v>44</v>
+      </c>
+      <c r="E5">
+        <v>6</v>
+      </c>
+      <c r="F5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" t="s">
+        <v>59</v>
+      </c>
+      <c r="B6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6" t="s">
+        <v>5</v>
+      </c>
+      <c r="D6" t="s">
+        <v>44</v>
+      </c>
+      <c r="E6">
+        <v>23</v>
+      </c>
+      <c r="F6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" t="s">
+        <v>60</v>
+      </c>
+      <c r="B7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D7" t="s">
+        <v>44</v>
+      </c>
+      <c r="E7">
+        <v>10</v>
+      </c>
+      <c r="F7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" t="s">
+        <v>61</v>
+      </c>
+      <c r="B8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" t="s">
         <v>45</v>
       </c>
-      <c r="D2">
+      <c r="E8">
+        <v>29</v>
+      </c>
+      <c r="F8">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" t="s">
+        <v>62</v>
+      </c>
+      <c r="B9" t="s">
+        <v>29</v>
+      </c>
+      <c r="C9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9" t="s">
+        <v>45</v>
+      </c>
+      <c r="E9">
+        <v>28</v>
+      </c>
+      <c r="F9">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" t="s">
+        <v>63</v>
+      </c>
+      <c r="B10" t="s">
+        <v>30</v>
+      </c>
+      <c r="C10" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" t="s">
+        <v>45</v>
+      </c>
+      <c r="E10">
+        <v>21</v>
+      </c>
+      <c r="F10">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" t="s">
+        <v>64</v>
+      </c>
+      <c r="B11" t="s">
+        <v>31</v>
+      </c>
+      <c r="C11" t="s">
+        <v>10</v>
+      </c>
+      <c r="D11" t="s">
+        <v>45</v>
+      </c>
+      <c r="E11">
+        <v>21</v>
+      </c>
+      <c r="F11">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" t="s">
+        <v>65</v>
+      </c>
+      <c r="B12" t="s">
+        <v>32</v>
+      </c>
+      <c r="C12" t="s">
+        <v>11</v>
+      </c>
+      <c r="D12" t="s">
+        <v>45</v>
+      </c>
+      <c r="E12">
+        <v>20</v>
+      </c>
+      <c r="F12">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" t="s">
+        <v>66</v>
+      </c>
+      <c r="B13" t="s">
+        <v>33</v>
+      </c>
+      <c r="C13" t="s">
+        <v>12</v>
+      </c>
+      <c r="D13" t="s">
+        <v>46</v>
+      </c>
+      <c r="E13">
+        <v>29</v>
+      </c>
+      <c r="F13">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" t="s">
+        <v>67</v>
+      </c>
+      <c r="B14" t="s">
+        <v>35</v>
+      </c>
+      <c r="C14" t="s">
+        <v>13</v>
+      </c>
+      <c r="D14" t="s">
+        <v>46</v>
+      </c>
+      <c r="E14">
+        <v>28</v>
+      </c>
+      <c r="F14">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" t="s">
+        <v>68</v>
+      </c>
+      <c r="B15" t="s">
+        <v>34</v>
+      </c>
+      <c r="C15" t="s">
+        <v>14</v>
+      </c>
+      <c r="D15" t="s">
+        <v>46</v>
+      </c>
+      <c r="E15">
+        <v>9</v>
+      </c>
+      <c r="F15">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" t="s">
+        <v>69</v>
+      </c>
+      <c r="B16" t="s">
+        <v>36</v>
+      </c>
+      <c r="C16" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" t="s">
-        <v>45</v>
-      </c>
-      <c r="D3">
+      <c r="D16" t="s">
+        <v>47</v>
+      </c>
+      <c r="E16">
+        <v>32</v>
+      </c>
+      <c r="F16">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17" t="s">
+        <v>70</v>
+      </c>
+      <c r="B17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C17" t="s">
+        <v>16</v>
+      </c>
+      <c r="D17" t="s">
+        <v>47</v>
+      </c>
+      <c r="E17">
+        <v>32</v>
+      </c>
+      <c r="F17">
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
-      <c r="A4" t="s">
-        <v>25</v>
-      </c>
-      <c r="B4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D4">
+    <row r="18" spans="1:6">
+      <c r="A18" t="s">
+        <v>71</v>
+      </c>
+      <c r="B18" t="s">
+        <v>38</v>
+      </c>
+      <c r="C18" t="s">
+        <v>17</v>
+      </c>
+      <c r="D18" t="s">
+        <v>47</v>
+      </c>
+      <c r="E18">
+        <v>32</v>
+      </c>
+      <c r="F18">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
+      <c r="A19" t="s">
+        <v>72</v>
+      </c>
+      <c r="B19" t="s">
+        <v>39</v>
+      </c>
+      <c r="C19" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" t="s">
-        <v>26</v>
-      </c>
-      <c r="B5" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5" t="s">
-        <v>45</v>
-      </c>
-      <c r="D5">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" t="s">
+      <c r="D19" t="s">
+        <v>47</v>
+      </c>
+      <c r="E19">
+        <v>33</v>
+      </c>
+      <c r="F19">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="A20" t="s">
+        <v>73</v>
+      </c>
+      <c r="B20" t="s">
+        <v>40</v>
+      </c>
+      <c r="C20" t="s">
+        <v>19</v>
+      </c>
+      <c r="D20" t="s">
+        <v>48</v>
+      </c>
+      <c r="E20">
         <v>27</v>
       </c>
-      <c r="B6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C6" t="s">
-        <v>45</v>
-      </c>
-      <c r="D6">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7" t="s">
-        <v>28</v>
-      </c>
-      <c r="B7" t="s">
+      <c r="F20">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="A21" t="s">
+        <v>74</v>
+      </c>
+      <c r="B21" t="s">
+        <v>41</v>
+      </c>
+      <c r="C21" t="s">
+        <v>20</v>
+      </c>
+      <c r="D21" t="s">
+        <v>48</v>
+      </c>
+      <c r="E21">
+        <v>17</v>
+      </c>
+      <c r="F21">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
+      <c r="A22" t="s">
+        <v>75</v>
+      </c>
+      <c r="B22" t="s">
+        <v>42</v>
+      </c>
+      <c r="C22" t="s">
+        <v>21</v>
+      </c>
+      <c r="D22" t="s">
+        <v>48</v>
+      </c>
+      <c r="E22">
         <v>7</v>
       </c>
-      <c r="C7" t="s">
-        <v>45</v>
-      </c>
-      <c r="D7">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" t="s">
-        <v>29</v>
-      </c>
-      <c r="B8" t="s">
-        <v>8</v>
-      </c>
-      <c r="C8" t="s">
-        <v>46</v>
-      </c>
-      <c r="D8">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9" t="s">
-        <v>30</v>
-      </c>
-      <c r="B9" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" t="s">
-        <v>46</v>
-      </c>
-      <c r="D9">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" t="s">
-        <v>31</v>
-      </c>
-      <c r="B10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C10" t="s">
-        <v>46</v>
-      </c>
-      <c r="D10">
+      <c r="F22">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
+      <c r="A23" t="s">
+        <v>76</v>
+      </c>
+      <c r="B23" t="s">
+        <v>50</v>
+      </c>
+      <c r="C23" t="s">
+        <v>51</v>
+      </c>
+      <c r="D23" t="s">
+        <v>49</v>
+      </c>
+      <c r="E23">
+        <v>200</v>
+      </c>
+      <c r="F23">
         <v>21</v>
       </c>
     </row>
-    <row r="11" spans="1:4">
-      <c r="A11" t="s">
-        <v>32</v>
-      </c>
-      <c r="B11" t="s">
-        <v>11</v>
-      </c>
-      <c r="C11" t="s">
-        <v>46</v>
-      </c>
-      <c r="D11">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="A12" t="s">
-        <v>33</v>
-      </c>
-      <c r="B12" t="s">
-        <v>12</v>
-      </c>
-      <c r="C12" t="s">
-        <v>46</v>
-      </c>
-      <c r="D12">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4">
-      <c r="A13" t="s">
-        <v>34</v>
-      </c>
-      <c r="B13" t="s">
-        <v>13</v>
-      </c>
-      <c r="C13" t="s">
-        <v>47</v>
-      </c>
-      <c r="D13">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4">
-      <c r="A14" t="s">
-        <v>36</v>
-      </c>
-      <c r="B14" t="s">
-        <v>14</v>
-      </c>
-      <c r="C14" t="s">
-        <v>47</v>
-      </c>
-      <c r="D14">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4">
-      <c r="A15" t="s">
-        <v>35</v>
-      </c>
-      <c r="B15" t="s">
-        <v>15</v>
-      </c>
-      <c r="C15" t="s">
-        <v>47</v>
-      </c>
-      <c r="D15">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4">
-      <c r="A16" t="s">
-        <v>37</v>
-      </c>
-      <c r="B16" t="s">
-        <v>16</v>
-      </c>
-      <c r="C16" t="s">
-        <v>48</v>
-      </c>
-      <c r="D16">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4">
-      <c r="A17" t="s">
-        <v>38</v>
-      </c>
-      <c r="B17" t="s">
-        <v>17</v>
-      </c>
-      <c r="C17" t="s">
-        <v>48</v>
-      </c>
-      <c r="D17">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4">
-      <c r="A18" t="s">
-        <v>39</v>
-      </c>
-      <c r="B18" t="s">
-        <v>18</v>
-      </c>
-      <c r="C18" t="s">
-        <v>48</v>
-      </c>
-      <c r="D18">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4">
-      <c r="A19" t="s">
-        <v>40</v>
-      </c>
-      <c r="B19" t="s">
-        <v>19</v>
-      </c>
-      <c r="C19" t="s">
-        <v>48</v>
-      </c>
-      <c r="D19">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4">
-      <c r="A20" t="s">
-        <v>41</v>
-      </c>
-      <c r="B20" t="s">
-        <v>20</v>
-      </c>
-      <c r="C20" t="s">
-        <v>49</v>
-      </c>
-      <c r="D20">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4">
-      <c r="A21" t="s">
-        <v>42</v>
-      </c>
-      <c r="B21" t="s">
-        <v>21</v>
-      </c>
-      <c r="C21" t="s">
-        <v>49</v>
-      </c>
-      <c r="D21">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4">
-      <c r="A22" t="s">
-        <v>43</v>
-      </c>
-      <c r="B22" t="s">
-        <v>22</v>
-      </c>
-      <c r="C22" t="s">
-        <v>49</v>
-      </c>
-      <c r="D22">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4">
-      <c r="A23" t="s">
-        <v>51</v>
-      </c>
-      <c r="B23" t="s">
-        <v>52</v>
-      </c>
-      <c r="C23" t="s">
-        <v>50</v>
-      </c>
-      <c r="D23">
-        <v>200</v>
-      </c>
-    </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/db/tablas_procesadas/Curso.xlsx
+++ b/db/tablas_procesadas/Curso.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PosGrado\Proyecto Titulacion\Timetabling\db\tablas_procesadas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70D425EA-C16C-47B3-B952-5C8C3D663097}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5045B888-EF06-4E97-B0E7-7F099690AFBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7965" yWindow="3480" windowWidth="28785" windowHeight="15345" xr2:uid="{BF92CB84-5E73-48F7-873C-5BA243B34C6E}"/>
+    <workbookView xWindow="4800" yWindow="5640" windowWidth="28785" windowHeight="15345" xr2:uid="{BF92CB84-5E73-48F7-873C-5BA243B34C6E}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -34,10 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="78">
-  <si>
-    <t>curso_id</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="74">
   <si>
     <t>1°Infantil (A)</t>
   </si>
@@ -183,15 +180,6 @@
     <t>Intermedio</t>
   </si>
   <si>
-    <t>3°Ini-3°Int</t>
-  </si>
-  <si>
-    <t>Orquestal</t>
-  </si>
-  <si>
-    <t>Orquesta</t>
-  </si>
-  <si>
     <t>inscritos</t>
   </si>
   <si>
@@ -264,10 +252,10 @@
     <t>G21</t>
   </si>
   <si>
-    <t>G22</t>
-  </si>
-  <si>
-    <t>contar</t>
+    <t>id_curso</t>
+  </si>
+  <si>
+    <t>pos_curso</t>
   </si>
 </sst>
 </file>
@@ -309,8 +297,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -645,45 +634,46 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3253D992-7E52-448D-BED3-7C5D72D55D53}">
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25"/>
   <cols>
     <col min="3" max="3" width="13" customWidth="1"/>
+    <col min="4" max="4" width="28.125" customWidth="1"/>
     <col min="5" max="5" width="14.625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="B1" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="C1" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="D1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E1" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="F1" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="B2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E2">
         <v>15</v>
@@ -694,16 +684,16 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="B3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E3">
         <v>15</v>
@@ -714,16 +704,16 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="B4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E4">
         <v>18</v>
@@ -734,16 +724,16 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="B5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E5">
         <v>6</v>
@@ -754,16 +744,16 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="B6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E6">
         <v>23</v>
@@ -774,16 +764,16 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="B7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E7">
         <v>10</v>
@@ -794,16 +784,16 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="B8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E8">
         <v>29</v>
@@ -814,16 +804,16 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="B9" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D9" t="s">
-        <v>45</v>
+        <v>7</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>44</v>
       </c>
       <c r="E9">
         <v>28</v>
@@ -834,16 +824,16 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="B10" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C10" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D10" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E10">
         <v>21</v>
@@ -854,16 +844,16 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="B11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C11" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D11" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E11">
         <v>21</v>
@@ -874,16 +864,16 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="B12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C12" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D12" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E12">
         <v>20</v>
@@ -894,16 +884,16 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="B13" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C13" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D13" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E13">
         <v>29</v>
@@ -914,16 +904,16 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B14" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C14" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D14" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E14">
         <v>28</v>
@@ -934,16 +924,16 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="B15" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C15" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D15" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E15">
         <v>9</v>
@@ -954,16 +944,16 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B16" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C16" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D16" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E16">
         <v>32</v>
@@ -974,16 +964,16 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="B17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C17" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D17" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E17">
         <v>32</v>
@@ -994,16 +984,16 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B18" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C18" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D18" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E18">
         <v>32</v>
@@ -1014,16 +1004,16 @@
     </row>
     <row r="19" spans="1:6">
       <c r="A19" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="B19" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C19" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D19" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E19">
         <v>33</v>
@@ -1034,16 +1024,16 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="B20" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C20" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D20" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E20">
         <v>27</v>
@@ -1054,16 +1044,16 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="B21" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C21" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D21" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E21">
         <v>17</v>
@@ -1074,42 +1064,22 @@
     </row>
     <row r="22" spans="1:6">
       <c r="A22" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="B22" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C22" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D22" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E22">
         <v>7</v>
       </c>
       <c r="F22">
         <v>20</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23" t="s">
-        <v>76</v>
-      </c>
-      <c r="B23" t="s">
-        <v>50</v>
-      </c>
-      <c r="C23" t="s">
-        <v>51</v>
-      </c>
-      <c r="D23" t="s">
-        <v>49</v>
-      </c>
-      <c r="E23">
-        <v>200</v>
-      </c>
-      <c r="F23">
-        <v>21</v>
       </c>
     </row>
   </sheetData>
